--- a/back/storage/app/ads/2026-08/Agustus-Format.xlsx
+++ b/back/storage/app/ads/2026-08/Agustus-Format.xlsx
@@ -1,13 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pulse-kembaliapps\ads-performance\back\storage\app\ads\2026-08\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F4FBE7-DA52-42DE-86FA-26D9D31E68A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Raw Data Report" r:id="rId3" sheetId="1"/>
+    <sheet name="Raw Data Report" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -167,57 +175,44 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <u val="none"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <u val="none"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <b val="true"/>
-      <u val="none"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor rgb="FFFFFF"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -228,249 +223,37 @@
     <border>
       <left/>
       <right/>
-      <top>
-        <color rgb="000000"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
+      <left style="thin">
+        <color rgb="FF90949C"/>
       </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <top>
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
+      <right style="thin">
+        <color rgb="FF90949C"/>
       </right>
       <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom>
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
+        <color rgb="FF90949C"/>
       </top>
       <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="90949C"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
+        <color rgb="FF90949C"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="90949C"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="90949C"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="90949C"/>
-      </left>
-      <right style="thin">
-        <color rgb="90949C"/>
-      </right>
-      <top style="thin">
-        <color rgb="90949C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="90949C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right>
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left>
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000000"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -479,80 +262,357 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="15" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="15" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="18" xfId="0" applyAlignment="true" applyFill="true" applyFont="true" applyNumberFormat="true" applyBorder="true">
-      <alignment vertical="center" horizontal="left" wrapText="false"/>
-      <protection locked="true"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q87"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultColWidth="12.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="18" max="16384" style="1" width="12.7109375"/>
-    <col min="17" max="17" style="1" width="23.4375" customWidth="true"/>
-    <col min="16" max="16" style="1" width="23.4375" customWidth="true"/>
-    <col min="15" max="15" style="1" width="23.4375" customWidth="true"/>
-    <col min="14" max="14" style="1" width="23.4375" customWidth="true"/>
-    <col min="13" max="13" style="1" width="23.4375" customWidth="true"/>
-    <col min="12" max="12" style="1" width="23.4375" customWidth="true"/>
-    <col min="11" max="11" style="1" width="23.4375" customWidth="true"/>
-    <col min="10" max="10" style="1" width="23.4375" customWidth="true"/>
-    <col min="9" max="9" style="1" width="23.4375" customWidth="true"/>
-    <col min="8" max="8" style="1" width="23.4375" customWidth="true"/>
-    <col min="7" max="7" style="1" width="23.4375" customWidth="true"/>
-    <col min="6" max="6" style="1" width="23.4375" customWidth="true"/>
-    <col min="5" max="5" style="1" width="23.4375" customWidth="true"/>
-    <col min="4" max="4" style="1" width="23.4375" customWidth="true"/>
-    <col min="3" max="3" style="1" width="23.4375" customWidth="true"/>
-    <col min="2" max="2" style="1" width="23.4375" customWidth="true"/>
-    <col min="1" max="1" width="58.59375" style="1" customWidth="true"/>
+    <col min="1" max="1" width="58.6328125" style="1" customWidth="1"/>
+    <col min="2" max="17" width="23.453125" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="12.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -605,7 +665,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
@@ -621,14 +681,14 @@
       <c r="E2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="7" t="n">
-        <v>62.0</v>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>84.0</v>
-      </c>
-      <c r="H2" s="6" t="n">
-        <v>1.35483871</v>
+      <c r="F2" s="7">
+        <v>62</v>
+      </c>
+      <c r="G2" s="7">
+        <v>84</v>
+      </c>
+      <c r="H2" s="6">
+        <v>1.3548387099999999</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>22</v>
@@ -636,17 +696,17 @@
       <c r="J2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="8" t="n">
-        <v>3273.0</v>
+      <c r="K2" s="8">
+        <v>3273</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="6" t="n">
-        <v>88.0</v>
-      </c>
-      <c r="N2" s="6" t="n">
-        <v>0.0</v>
+      <c r="M2" s="6">
+        <v>88</v>
+      </c>
+      <c r="N2" s="6">
+        <v>0</v>
       </c>
       <c r="O2" s="9" t="s">
         <v>18</v>
@@ -658,7 +718,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
@@ -674,13 +734,13 @@
       <c r="E3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="7" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>41.0</v>
-      </c>
-      <c r="H3" s="6" t="n">
+      <c r="F3" s="7">
+        <v>28</v>
+      </c>
+      <c r="G3" s="7">
+        <v>41</v>
+      </c>
+      <c r="H3" s="6">
         <v>1.46428571</v>
       </c>
       <c r="I3" s="6" t="s">
@@ -689,17 +749,17 @@
       <c r="J3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="8" t="n">
-        <v>2597.0</v>
+      <c r="K3" s="8">
+        <v>2597</v>
       </c>
       <c r="L3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="6" t="n">
-        <v>41.0</v>
-      </c>
-      <c r="N3" s="6" t="n">
-        <v>0.0</v>
+      <c r="M3" s="6">
+        <v>41</v>
+      </c>
+      <c r="N3" s="6">
+        <v>0</v>
       </c>
       <c r="O3" s="9" t="s">
         <v>18</v>
@@ -711,7 +771,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
@@ -727,13 +787,13 @@
       <c r="E4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="7" t="n">
-        <v>191.0</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>236.0</v>
-      </c>
-      <c r="H4" s="6" t="n">
+      <c r="F4" s="7">
+        <v>191</v>
+      </c>
+      <c r="G4" s="7">
+        <v>236</v>
+      </c>
+      <c r="H4" s="6">
         <v>1.23560209</v>
       </c>
       <c r="I4" s="6" t="s">
@@ -742,17 +802,17 @@
       <c r="J4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="8" t="n">
-        <v>13391.0</v>
+      <c r="K4" s="8">
+        <v>13391</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="6" t="n">
-        <v>213.0</v>
-      </c>
-      <c r="N4" s="6" t="n">
-        <v>1.0</v>
+      <c r="M4" s="6">
+        <v>213</v>
+      </c>
+      <c r="N4" s="6">
+        <v>1</v>
       </c>
       <c r="O4" s="9" t="s">
         <v>18</v>
@@ -764,7 +824,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
@@ -780,32 +840,32 @@
       <c r="E5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="7" t="n">
-        <v>76.0</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>85.0</v>
-      </c>
-      <c r="H5" s="6" t="n">
+      <c r="F5" s="7">
+        <v>76</v>
+      </c>
+      <c r="G5" s="7">
+        <v>85</v>
+      </c>
+      <c r="H5" s="6">
         <v>1.11842105</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>8526.0</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>8526.0</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>86.0</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>2.0</v>
+      <c r="J5" s="6">
+        <v>1</v>
+      </c>
+      <c r="K5" s="8">
+        <v>8526</v>
+      </c>
+      <c r="L5" s="8">
+        <v>8526</v>
+      </c>
+      <c r="M5" s="6">
+        <v>86</v>
+      </c>
+      <c r="N5" s="6">
+        <v>2</v>
       </c>
       <c r="O5" s="9" t="s">
         <v>18</v>
@@ -817,7 +877,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
@@ -833,32 +893,32 @@
       <c r="E6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="7" t="n">
-        <v>194.0</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>264.0</v>
-      </c>
-      <c r="H6" s="6" t="n">
+      <c r="F6" s="7">
+        <v>194</v>
+      </c>
+      <c r="G6" s="7">
+        <v>264</v>
+      </c>
+      <c r="H6" s="6">
         <v>1.36082474</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K6" s="8" t="n">
-        <v>24799.0</v>
-      </c>
-      <c r="L6" s="8" t="n">
-        <v>24799.0</v>
-      </c>
-      <c r="M6" s="6" t="n">
-        <v>249.0</v>
-      </c>
-      <c r="N6" s="6" t="n">
-        <v>8.0</v>
+      <c r="J6" s="6">
+        <v>1</v>
+      </c>
+      <c r="K6" s="8">
+        <v>24799</v>
+      </c>
+      <c r="L6" s="8">
+        <v>24799</v>
+      </c>
+      <c r="M6" s="6">
+        <v>249</v>
+      </c>
+      <c r="N6" s="6">
+        <v>8</v>
       </c>
       <c r="O6" s="9" t="s">
         <v>27</v>
@@ -870,7 +930,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
@@ -886,14 +946,14 @@
       <c r="E7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="7" t="n">
-        <v>47.0</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>61.0</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>1.29787234</v>
+      <c r="F7" s="7">
+        <v>47</v>
+      </c>
+      <c r="G7" s="7">
+        <v>61</v>
+      </c>
+      <c r="H7" s="6">
+        <v>1.2978723400000001</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>22</v>
@@ -901,17 +961,17 @@
       <c r="J7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="8" t="n">
-        <v>5200.0</v>
+      <c r="K7" s="8">
+        <v>5200</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M7" s="6" t="n">
-        <v>67.0</v>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>1.0</v>
+      <c r="M7" s="6">
+        <v>67</v>
+      </c>
+      <c r="N7" s="6">
+        <v>1</v>
       </c>
       <c r="O7" s="9" t="s">
         <v>27</v>
@@ -923,7 +983,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
@@ -939,13 +999,13 @@
       <c r="E8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="7" t="n">
-        <v>521.0</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>672.0</v>
-      </c>
-      <c r="H8" s="6" t="n">
+      <c r="F8" s="7">
+        <v>521</v>
+      </c>
+      <c r="G8" s="7">
+        <v>672</v>
+      </c>
+      <c r="H8" s="6">
         <v>1.28982726</v>
       </c>
       <c r="I8" s="6" t="s">
@@ -954,17 +1014,17 @@
       <c r="J8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="8" t="n">
-        <v>36421.0</v>
+      <c r="K8" s="8">
+        <v>36421</v>
       </c>
       <c r="L8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M8" s="6" t="n">
-        <v>663.0</v>
-      </c>
-      <c r="N8" s="6" t="n">
-        <v>9.0</v>
+      <c r="M8" s="6">
+        <v>663</v>
+      </c>
+      <c r="N8" s="6">
+        <v>9</v>
       </c>
       <c r="O8" s="9" t="s">
         <v>27</v>
@@ -976,7 +1036,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
@@ -992,13 +1052,13 @@
       <c r="E9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="7" t="n">
-        <v>290.0</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>301.0</v>
-      </c>
-      <c r="H9" s="6" t="n">
+      <c r="F9" s="7">
+        <v>290</v>
+      </c>
+      <c r="G9" s="7">
+        <v>301</v>
+      </c>
+      <c r="H9" s="6">
         <v>1.03793103</v>
       </c>
       <c r="I9" s="6" t="s">
@@ -1007,17 +1067,17 @@
       <c r="J9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K9" s="8" t="n">
-        <v>7267.0</v>
+      <c r="K9" s="8">
+        <v>7267</v>
       </c>
       <c r="L9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M9" s="6" t="n">
-        <v>309.0</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>3.0</v>
+      <c r="M9" s="6">
+        <v>309</v>
+      </c>
+      <c r="N9" s="6">
+        <v>3</v>
       </c>
       <c r="O9" s="9" t="s">
         <v>27</v>
@@ -1029,7 +1089,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>17</v>
       </c>
@@ -1045,13 +1105,13 @@
       <c r="E10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="7" t="n">
-        <v>230.0</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>242.0</v>
-      </c>
-      <c r="H10" s="6" t="n">
+      <c r="F10" s="7">
+        <v>230</v>
+      </c>
+      <c r="G10" s="7">
+        <v>242</v>
+      </c>
+      <c r="H10" s="6">
         <v>1.05217391</v>
       </c>
       <c r="I10" s="6" t="s">
@@ -1060,17 +1120,17 @@
       <c r="J10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K10" s="8" t="n">
-        <v>7205.0</v>
+      <c r="K10" s="8">
+        <v>7205</v>
       </c>
       <c r="L10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M10" s="6" t="n">
-        <v>236.0</v>
-      </c>
-      <c r="N10" s="6" t="n">
-        <v>3.0</v>
+      <c r="M10" s="6">
+        <v>236</v>
+      </c>
+      <c r="N10" s="6">
+        <v>3</v>
       </c>
       <c r="O10" s="9" t="s">
         <v>28</v>
@@ -1082,7 +1142,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
@@ -1098,13 +1158,13 @@
       <c r="E11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="7" t="n">
-        <v>365.0</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>503.0</v>
-      </c>
-      <c r="H11" s="6" t="n">
+      <c r="F11" s="7">
+        <v>365</v>
+      </c>
+      <c r="G11" s="7">
+        <v>503</v>
+      </c>
+      <c r="H11" s="6">
         <v>1.37808219</v>
       </c>
       <c r="I11" s="6" t="s">
@@ -1113,17 +1173,17 @@
       <c r="J11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="8" t="n">
-        <v>31770.0</v>
+      <c r="K11" s="8">
+        <v>31770</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="6" t="n">
-        <v>474.0</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>2.0</v>
+      <c r="M11" s="6">
+        <v>474</v>
+      </c>
+      <c r="N11" s="6">
+        <v>2</v>
       </c>
       <c r="O11" s="9" t="s">
         <v>28</v>
@@ -1135,7 +1195,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>17</v>
       </c>
@@ -1151,13 +1211,13 @@
       <c r="E12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="7" t="n">
-        <v>26.0</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>39.0</v>
-      </c>
-      <c r="H12" s="6" t="n">
+      <c r="F12" s="7">
+        <v>26</v>
+      </c>
+      <c r="G12" s="7">
+        <v>39</v>
+      </c>
+      <c r="H12" s="6">
         <v>1.5</v>
       </c>
       <c r="I12" s="6" t="s">
@@ -1166,17 +1226,17 @@
       <c r="J12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K12" s="8" t="n">
-        <v>5348.0</v>
+      <c r="K12" s="8">
+        <v>5348</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M12" s="6" t="n">
-        <v>32.0</v>
-      </c>
-      <c r="N12" s="6" t="n">
-        <v>0.0</v>
+      <c r="M12" s="6">
+        <v>32</v>
+      </c>
+      <c r="N12" s="6">
+        <v>0</v>
       </c>
       <c r="O12" s="9" t="s">
         <v>28</v>
@@ -1188,7 +1248,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
@@ -1204,32 +1264,32 @@
       <c r="E13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="7" t="n">
-        <v>177.0</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>245.0</v>
-      </c>
-      <c r="H13" s="6" t="n">
+      <c r="F13" s="7">
+        <v>177</v>
+      </c>
+      <c r="G13" s="7">
+        <v>245</v>
+      </c>
+      <c r="H13" s="6">
         <v>1.38418079</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J13" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K13" s="8" t="n">
-        <v>24067.0</v>
-      </c>
-      <c r="L13" s="8" t="n">
-        <v>24067.0</v>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>244.0</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>10.0</v>
+      <c r="J13" s="6">
+        <v>1</v>
+      </c>
+      <c r="K13" s="8">
+        <v>24067</v>
+      </c>
+      <c r="L13" s="8">
+        <v>24067</v>
+      </c>
+      <c r="M13" s="6">
+        <v>244</v>
+      </c>
+      <c r="N13" s="6">
+        <v>10</v>
       </c>
       <c r="O13" s="9" t="s">
         <v>28</v>
@@ -1241,7 +1301,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>17</v>
       </c>
@@ -1257,32 +1317,32 @@
       <c r="E14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="7" t="n">
-        <v>212.0</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>288.0</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>1.35849057</v>
+      <c r="F14" s="7">
+        <v>212</v>
+      </c>
+      <c r="G14" s="7">
+        <v>288</v>
+      </c>
+      <c r="H14" s="6">
+        <v>1.3584905700000001</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>22637.0</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>22637.0</v>
-      </c>
-      <c r="M14" s="6" t="n">
-        <v>279.0</v>
-      </c>
-      <c r="N14" s="6" t="n">
-        <v>6.0</v>
+      <c r="J14" s="6">
+        <v>1</v>
+      </c>
+      <c r="K14" s="8">
+        <v>22637</v>
+      </c>
+      <c r="L14" s="8">
+        <v>22637</v>
+      </c>
+      <c r="M14" s="6">
+        <v>279</v>
+      </c>
+      <c r="N14" s="6">
+        <v>6</v>
       </c>
       <c r="O14" s="9" t="s">
         <v>29</v>
@@ -1294,7 +1354,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
@@ -1310,14 +1370,14 @@
       <c r="E15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="7" t="n">
-        <v>37.0</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>61.0</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>1.64864865</v>
+      <c r="F15" s="7">
+        <v>37</v>
+      </c>
+      <c r="G15" s="7">
+        <v>61</v>
+      </c>
+      <c r="H15" s="6">
+        <v>1.6486486499999999</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>22</v>
@@ -1325,17 +1385,17 @@
       <c r="J15" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K15" s="8" t="n">
-        <v>9621.0</v>
+      <c r="K15" s="8">
+        <v>9621</v>
       </c>
       <c r="L15" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M15" s="6" t="n">
-        <v>59.0</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>3.0</v>
+      <c r="M15" s="6">
+        <v>59</v>
+      </c>
+      <c r="N15" s="6">
+        <v>3</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>29</v>
@@ -1347,7 +1407,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>17</v>
       </c>
@@ -1363,32 +1423,32 @@
       <c r="E16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="7" t="n">
-        <v>433.0</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>610.0</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>1.40877598</v>
+      <c r="F16" s="7">
+        <v>433</v>
+      </c>
+      <c r="G16" s="7">
+        <v>610</v>
+      </c>
+      <c r="H16" s="6">
+        <v>1.4087759799999999</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J16" s="6" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="K16" s="8" t="n">
-        <v>40907.0</v>
-      </c>
-      <c r="L16" s="8" t="n">
+      <c r="J16" s="6">
+        <v>4</v>
+      </c>
+      <c r="K16" s="8">
+        <v>40907</v>
+      </c>
+      <c r="L16" s="8">
         <v>10226.75</v>
       </c>
-      <c r="M16" s="6" t="n">
-        <v>634.0</v>
-      </c>
-      <c r="N16" s="6" t="n">
-        <v>12.0</v>
+      <c r="M16" s="6">
+        <v>634</v>
+      </c>
+      <c r="N16" s="6">
+        <v>12</v>
       </c>
       <c r="O16" s="9" t="s">
         <v>29</v>
@@ -1400,7 +1460,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>17</v>
       </c>
@@ -1416,32 +1476,32 @@
       <c r="E17" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="7" t="n">
-        <v>236.0</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>262.0</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>1.11016949</v>
+      <c r="F17" s="7">
+        <v>236</v>
+      </c>
+      <c r="G17" s="7">
+        <v>262</v>
+      </c>
+      <c r="H17" s="6">
+        <v>1.1101694900000001</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J17" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>7081.0</v>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>7081.0</v>
-      </c>
-      <c r="M17" s="6" t="n">
-        <v>265.0</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>1.0</v>
+      <c r="J17" s="6">
+        <v>1</v>
+      </c>
+      <c r="K17" s="8">
+        <v>7081</v>
+      </c>
+      <c r="L17" s="8">
+        <v>7081</v>
+      </c>
+      <c r="M17" s="6">
+        <v>265</v>
+      </c>
+      <c r="N17" s="6">
+        <v>1</v>
       </c>
       <c r="O17" s="9" t="s">
         <v>29</v>
@@ -1453,7 +1513,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
@@ -1469,14 +1529,14 @@
       <c r="E18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="7" t="n">
-        <v>321.0</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>407.0</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>1.26791277</v>
+      <c r="F18" s="7">
+        <v>321</v>
+      </c>
+      <c r="G18" s="7">
+        <v>407</v>
+      </c>
+      <c r="H18" s="6">
+        <v>1.2679127699999999</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>22</v>
@@ -1484,17 +1544,17 @@
       <c r="J18" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="8" t="n">
-        <v>21161.0</v>
+      <c r="K18" s="8">
+        <v>21161</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M18" s="6" t="n">
-        <v>394.0</v>
-      </c>
-      <c r="N18" s="6" t="n">
-        <v>4.0</v>
+      <c r="M18" s="6">
+        <v>394</v>
+      </c>
+      <c r="N18" s="6">
+        <v>4</v>
       </c>
       <c r="O18" s="9" t="s">
         <v>30</v>
@@ -1506,7 +1566,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>17</v>
       </c>
@@ -1522,14 +1582,14 @@
       <c r="E19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F19" s="7" t="n">
-        <v>51.0</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>65.0</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>1.2745098</v>
+      <c r="F19" s="7">
+        <v>51</v>
+      </c>
+      <c r="G19" s="7">
+        <v>65</v>
+      </c>
+      <c r="H19" s="6">
+        <v>1.2745097999999999</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>22</v>
@@ -1537,17 +1597,17 @@
       <c r="J19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K19" s="8" t="n">
-        <v>5073.0</v>
+      <c r="K19" s="8">
+        <v>5073</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M19" s="6" t="n">
-        <v>65.0</v>
-      </c>
-      <c r="N19" s="6" t="n">
-        <v>1.0</v>
+      <c r="M19" s="6">
+        <v>65</v>
+      </c>
+      <c r="N19" s="6">
+        <v>1</v>
       </c>
       <c r="O19" s="9" t="s">
         <v>30</v>
@@ -1559,7 +1619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>17</v>
       </c>
@@ -1575,14 +1635,14 @@
       <c r="E20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="7" t="n">
-        <v>463.0</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>573.0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>1.23758099</v>
+      <c r="F20" s="7">
+        <v>463</v>
+      </c>
+      <c r="G20" s="7">
+        <v>573</v>
+      </c>
+      <c r="H20" s="6">
+        <v>1.2375809900000001</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>22</v>
@@ -1590,17 +1650,17 @@
       <c r="J20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K20" s="8" t="n">
-        <v>35516.0</v>
+      <c r="K20" s="8">
+        <v>35516</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M20" s="6" t="n">
-        <v>578.0</v>
-      </c>
-      <c r="N20" s="6" t="n">
-        <v>9.0</v>
+      <c r="M20" s="6">
+        <v>578</v>
+      </c>
+      <c r="N20" s="6">
+        <v>9</v>
       </c>
       <c r="O20" s="9" t="s">
         <v>30</v>
@@ -1612,7 +1672,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>17</v>
       </c>
@@ -1628,14 +1688,14 @@
       <c r="E21" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F21" s="7" t="n">
-        <v>367.0</v>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>409.0</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>1.11444142</v>
+      <c r="F21" s="7">
+        <v>367</v>
+      </c>
+      <c r="G21" s="7">
+        <v>409</v>
+      </c>
+      <c r="H21" s="6">
+        <v>1.1144414199999999</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>22</v>
@@ -1643,17 +1703,17 @@
       <c r="J21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K21" s="8" t="n">
-        <v>8646.0</v>
+      <c r="K21" s="8">
+        <v>8646</v>
       </c>
       <c r="L21" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M21" s="6" t="n">
-        <v>416.0</v>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>2.0</v>
+      <c r="M21" s="6">
+        <v>416</v>
+      </c>
+      <c r="N21" s="6">
+        <v>2</v>
       </c>
       <c r="O21" s="9" t="s">
         <v>30</v>
@@ -1665,7 +1725,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
@@ -1681,13 +1741,13 @@
       <c r="E22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="7" t="n">
-        <v>344.0</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>423.0</v>
-      </c>
-      <c r="H22" s="6" t="n">
+      <c r="F22" s="7">
+        <v>344</v>
+      </c>
+      <c r="G22" s="7">
+        <v>423</v>
+      </c>
+      <c r="H22" s="6">
         <v>1.22965116</v>
       </c>
       <c r="I22" s="6" t="s">
@@ -1696,17 +1756,17 @@
       <c r="J22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K22" s="8" t="n">
-        <v>22993.0</v>
+      <c r="K22" s="8">
+        <v>22993</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M22" s="6" t="n">
-        <v>422.0</v>
-      </c>
-      <c r="N22" s="6" t="n">
-        <v>3.0</v>
+      <c r="M22" s="6">
+        <v>422</v>
+      </c>
+      <c r="N22" s="6">
+        <v>3</v>
       </c>
       <c r="O22" s="9" t="s">
         <v>31</v>
@@ -1718,7 +1778,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>17</v>
       </c>
@@ -1734,13 +1794,13 @@
       <c r="E23" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="7" t="n">
-        <v>415.0</v>
-      </c>
-      <c r="G23" s="7" t="n">
-        <v>441.0</v>
-      </c>
-      <c r="H23" s="6" t="n">
+      <c r="F23" s="7">
+        <v>415</v>
+      </c>
+      <c r="G23" s="7">
+        <v>441</v>
+      </c>
+      <c r="H23" s="6">
         <v>1.0626506</v>
       </c>
       <c r="I23" s="6" t="s">
@@ -1749,17 +1809,17 @@
       <c r="J23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K23" s="8" t="n">
-        <v>7668.0</v>
+      <c r="K23" s="8">
+        <v>7668</v>
       </c>
       <c r="L23" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M23" s="6" t="n">
-        <v>443.0</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>1.0</v>
+      <c r="M23" s="6">
+        <v>443</v>
+      </c>
+      <c r="N23" s="6">
+        <v>1</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>31</v>
@@ -1771,7 +1831,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>17</v>
       </c>
@@ -1787,14 +1847,14 @@
       <c r="E24" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="7" t="n">
-        <v>226.0</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>261.0</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>1.15486726</v>
+      <c r="F24" s="7">
+        <v>226</v>
+      </c>
+      <c r="G24" s="7">
+        <v>261</v>
+      </c>
+      <c r="H24" s="6">
+        <v>1.1548672600000001</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>22</v>
@@ -1802,17 +1862,17 @@
       <c r="J24" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="8" t="n">
-        <v>11368.0</v>
+      <c r="K24" s="8">
+        <v>11368</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M24" s="6" t="n">
-        <v>250.0</v>
-      </c>
-      <c r="N24" s="6" t="n">
-        <v>3.0</v>
+      <c r="M24" s="6">
+        <v>250</v>
+      </c>
+      <c r="N24" s="6">
+        <v>3</v>
       </c>
       <c r="O24" s="9" t="s">
         <v>31</v>
@@ -1824,7 +1884,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>17</v>
       </c>
@@ -1840,32 +1900,32 @@
       <c r="E25" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F25" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G25" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>0.0</v>
+      <c r="F25" s="7">
+        <v>0</v>
+      </c>
+      <c r="G25" s="7">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6">
+        <v>0</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J25" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K25" s="8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M25" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="N25" s="6" t="n">
-        <v>0.0</v>
+      <c r="J25" s="6">
+        <v>1</v>
+      </c>
+      <c r="K25" s="8">
+        <v>0</v>
+      </c>
+      <c r="L25" s="8">
+        <v>0</v>
+      </c>
+      <c r="M25" s="6">
+        <v>0</v>
+      </c>
+      <c r="N25" s="6">
+        <v>0</v>
       </c>
       <c r="O25" s="9" t="s">
         <v>31</v>
@@ -1877,7 +1937,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>17</v>
       </c>
@@ -1893,14 +1953,14 @@
       <c r="E26" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="7" t="n">
-        <v>84.0</v>
-      </c>
-      <c r="G26" s="7" t="n">
-        <v>115.0</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>1.36904762</v>
+      <c r="F26" s="7">
+        <v>84</v>
+      </c>
+      <c r="G26" s="7">
+        <v>115</v>
+      </c>
+      <c r="H26" s="6">
+        <v>1.3690476199999999</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>22</v>
@@ -1908,17 +1968,17 @@
       <c r="J26" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K26" s="8" t="n">
-        <v>8399.0</v>
+      <c r="K26" s="8">
+        <v>8399</v>
       </c>
       <c r="L26" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M26" s="6" t="n">
-        <v>106.0</v>
-      </c>
-      <c r="N26" s="6" t="n">
-        <v>3.0</v>
+      <c r="M26" s="6">
+        <v>106</v>
+      </c>
+      <c r="N26" s="6">
+        <v>3</v>
       </c>
       <c r="O26" s="9" t="s">
         <v>31</v>
@@ -1930,7 +1990,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>17</v>
       </c>
@@ -1946,32 +2006,32 @@
       <c r="E27" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="7" t="n">
-        <v>79.0</v>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>107.0</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>1.35443038</v>
+      <c r="F27" s="7">
+        <v>79</v>
+      </c>
+      <c r="G27" s="7">
+        <v>107</v>
+      </c>
+      <c r="H27" s="6">
+        <v>1.3544303799999999</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J27" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K27" s="8" t="n">
-        <v>5372.0</v>
-      </c>
-      <c r="L27" s="8" t="n">
-        <v>5372.0</v>
-      </c>
-      <c r="M27" s="6" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="N27" s="6" t="n">
-        <v>1.0</v>
+      <c r="J27" s="6">
+        <v>1</v>
+      </c>
+      <c r="K27" s="8">
+        <v>5372</v>
+      </c>
+      <c r="L27" s="8">
+        <v>5372</v>
+      </c>
+      <c r="M27" s="6">
+        <v>100</v>
+      </c>
+      <c r="N27" s="6">
+        <v>1</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>34</v>
@@ -1983,7 +2043,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>17</v>
       </c>
@@ -1999,14 +2059,14 @@
       <c r="E28" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="7" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>31.0</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>1.82352941</v>
+      <c r="F28" s="7">
+        <v>17</v>
+      </c>
+      <c r="G28" s="7">
+        <v>31</v>
+      </c>
+      <c r="H28" s="6">
+        <v>1.8235294099999999</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>22</v>
@@ -2014,17 +2074,17 @@
       <c r="J28" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K28" s="8" t="n">
-        <v>6646.0</v>
+      <c r="K28" s="8">
+        <v>6646</v>
       </c>
       <c r="L28" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M28" s="6" t="n">
-        <v>33.0</v>
-      </c>
-      <c r="N28" s="6" t="n">
-        <v>1.0</v>
+      <c r="M28" s="6">
+        <v>33</v>
+      </c>
+      <c r="N28" s="6">
+        <v>1</v>
       </c>
       <c r="O28" s="9" t="s">
         <v>34</v>
@@ -2036,7 +2096,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>17</v>
       </c>
@@ -2052,32 +2112,32 @@
       <c r="E29" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="7" t="n">
-        <v>4878.0</v>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>6010.0</v>
-      </c>
-      <c r="H29" s="6" t="n">
+      <c r="F29" s="7">
+        <v>4878</v>
+      </c>
+      <c r="G29" s="7">
+        <v>6010</v>
+      </c>
+      <c r="H29" s="6">
         <v>1.23206232</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J29" s="6" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="K29" s="8" t="n">
-        <v>68290.0</v>
-      </c>
-      <c r="L29" s="8" t="n">
+      <c r="J29" s="6">
+        <v>4</v>
+      </c>
+      <c r="K29" s="8">
+        <v>68290</v>
+      </c>
+      <c r="L29" s="8">
         <v>17072.5</v>
       </c>
-      <c r="M29" s="6" t="n">
-        <v>6144.0</v>
-      </c>
-      <c r="N29" s="6" t="n">
-        <v>47.0</v>
+      <c r="M29" s="6">
+        <v>6144</v>
+      </c>
+      <c r="N29" s="6">
+        <v>47</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>34</v>
@@ -2089,7 +2149,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>17</v>
       </c>
@@ -2105,13 +2165,13 @@
       <c r="E30" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="7" t="n">
-        <v>49.0</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>62.0</v>
-      </c>
-      <c r="H30" s="6" t="n">
+      <c r="F30" s="7">
+        <v>49</v>
+      </c>
+      <c r="G30" s="7">
+        <v>62</v>
+      </c>
+      <c r="H30" s="6">
         <v>1.26530612</v>
       </c>
       <c r="I30" s="6" t="s">
@@ -2120,17 +2180,17 @@
       <c r="J30" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K30" s="8" t="n">
-        <v>3245.0</v>
+      <c r="K30" s="8">
+        <v>3245</v>
       </c>
       <c r="L30" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M30" s="6" t="n">
-        <v>65.0</v>
-      </c>
-      <c r="N30" s="6" t="n">
-        <v>0.0</v>
+      <c r="M30" s="6">
+        <v>65</v>
+      </c>
+      <c r="N30" s="6">
+        <v>0</v>
       </c>
       <c r="O30" s="9" t="s">
         <v>34</v>
@@ -2142,7 +2202,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>17</v>
       </c>
@@ -2158,32 +2218,32 @@
       <c r="E31" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="7" t="n">
-        <v>340.0</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>364.0</v>
-      </c>
-      <c r="H31" s="6" t="n">
+      <c r="F31" s="7">
+        <v>340</v>
+      </c>
+      <c r="G31" s="7">
+        <v>364</v>
+      </c>
+      <c r="H31" s="6">
         <v>1.07058824</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J31" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K31" s="8" t="n">
-        <v>9129.0</v>
-      </c>
-      <c r="L31" s="8" t="n">
-        <v>9129.0</v>
-      </c>
-      <c r="M31" s="6" t="n">
-        <v>376.0</v>
-      </c>
-      <c r="N31" s="6" t="n">
-        <v>5.0</v>
+      <c r="J31" s="6">
+        <v>1</v>
+      </c>
+      <c r="K31" s="8">
+        <v>9129</v>
+      </c>
+      <c r="L31" s="8">
+        <v>9129</v>
+      </c>
+      <c r="M31" s="6">
+        <v>376</v>
+      </c>
+      <c r="N31" s="6">
+        <v>5</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>34</v>
@@ -2195,7 +2255,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>17</v>
       </c>
@@ -2211,32 +2271,32 @@
       <c r="E32" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F32" s="7" t="n">
-        <v>221.0</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>232.0</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>1.04977376</v>
+      <c r="F32" s="7">
+        <v>221</v>
+      </c>
+      <c r="G32" s="7">
+        <v>232</v>
+      </c>
+      <c r="H32" s="6">
+        <v>1.0497737599999999</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J32" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K32" s="8" t="n">
-        <v>7835.0</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>7835.0</v>
-      </c>
-      <c r="M32" s="6" t="n">
-        <v>235.0</v>
-      </c>
-      <c r="N32" s="6" t="n">
-        <v>3.0</v>
+      <c r="J32" s="6">
+        <v>1</v>
+      </c>
+      <c r="K32" s="8">
+        <v>7835</v>
+      </c>
+      <c r="L32" s="8">
+        <v>7835</v>
+      </c>
+      <c r="M32" s="6">
+        <v>235</v>
+      </c>
+      <c r="N32" s="6">
+        <v>3</v>
       </c>
       <c r="O32" s="9" t="s">
         <v>35</v>
@@ -2248,7 +2308,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>17</v>
       </c>
@@ -2264,14 +2324,14 @@
       <c r="E33" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="7" t="n">
-        <v>46.0</v>
-      </c>
-      <c r="G33" s="7" t="n">
-        <v>58.0</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>1.26086957</v>
+      <c r="F33" s="7">
+        <v>46</v>
+      </c>
+      <c r="G33" s="7">
+        <v>58</v>
+      </c>
+      <c r="H33" s="6">
+        <v>1.2608695700000001</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>22</v>
@@ -2279,17 +2339,17 @@
       <c r="J33" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K33" s="8" t="n">
-        <v>1552.0</v>
+      <c r="K33" s="8">
+        <v>1552</v>
       </c>
       <c r="L33" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M33" s="6" t="n">
-        <v>61.0</v>
-      </c>
-      <c r="N33" s="6" t="n">
-        <v>0.0</v>
+      <c r="M33" s="6">
+        <v>61</v>
+      </c>
+      <c r="N33" s="6">
+        <v>0</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>35</v>
@@ -2301,7 +2361,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>17</v>
       </c>
@@ -2317,14 +2377,14 @@
       <c r="E34" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F34" s="7" t="n">
-        <v>2641.0</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>3137.0</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>1.18780765</v>
+      <c r="F34" s="7">
+        <v>2641</v>
+      </c>
+      <c r="G34" s="7">
+        <v>3137</v>
+      </c>
+      <c r="H34" s="6">
+        <v>1.1878076500000001</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>22</v>
@@ -2332,17 +2392,17 @@
       <c r="J34" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K34" s="8" t="n">
-        <v>35940.0</v>
+      <c r="K34" s="8">
+        <v>35940</v>
       </c>
       <c r="L34" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M34" s="6" t="n">
-        <v>3178.0</v>
-      </c>
-      <c r="N34" s="6" t="n">
-        <v>15.0</v>
+      <c r="M34" s="6">
+        <v>3178</v>
+      </c>
+      <c r="N34" s="6">
+        <v>15</v>
       </c>
       <c r="O34" s="9" t="s">
         <v>35</v>
@@ -2354,7 +2414,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>17</v>
       </c>
@@ -2370,13 +2430,13 @@
       <c r="E35" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F35" s="7" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="G35" s="7" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="H35" s="6" t="n">
+      <c r="F35" s="7">
+        <v>14</v>
+      </c>
+      <c r="G35" s="7">
+        <v>19</v>
+      </c>
+      <c r="H35" s="6">
         <v>1.35714286</v>
       </c>
       <c r="I35" s="6" t="s">
@@ -2385,17 +2445,17 @@
       <c r="J35" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K35" s="8" t="n">
-        <v>2129.0</v>
+      <c r="K35" s="8">
+        <v>2129</v>
       </c>
       <c r="L35" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M35" s="6" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="N35" s="6" t="n">
-        <v>0.0</v>
+      <c r="M35" s="6">
+        <v>19</v>
+      </c>
+      <c r="N35" s="6">
+        <v>0</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>35</v>
@@ -2407,7 +2467,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>17</v>
       </c>
@@ -2423,32 +2483,32 @@
       <c r="E36" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F36" s="7" t="n">
-        <v>188.0</v>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>280.0</v>
-      </c>
-      <c r="H36" s="6" t="n">
-        <v>1.4893617</v>
+      <c r="F36" s="7">
+        <v>188</v>
+      </c>
+      <c r="G36" s="7">
+        <v>280</v>
+      </c>
+      <c r="H36" s="6">
+        <v>1.4893616999999999</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J36" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K36" s="8" t="n">
-        <v>29548.0</v>
-      </c>
-      <c r="L36" s="8" t="n">
-        <v>29548.0</v>
-      </c>
-      <c r="M36" s="6" t="n">
-        <v>284.0</v>
-      </c>
-      <c r="N36" s="6" t="n">
-        <v>7.0</v>
+      <c r="J36" s="6">
+        <v>1</v>
+      </c>
+      <c r="K36" s="8">
+        <v>29548</v>
+      </c>
+      <c r="L36" s="8">
+        <v>29548</v>
+      </c>
+      <c r="M36" s="6">
+        <v>284</v>
+      </c>
+      <c r="N36" s="6">
+        <v>7</v>
       </c>
       <c r="O36" s="9" t="s">
         <v>36</v>
@@ -2460,7 +2520,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>17</v>
       </c>
@@ -2476,32 +2536,32 @@
       <c r="E37" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F37" s="7" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="G37" s="7" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="H37" s="6" t="n">
+      <c r="F37" s="7">
+        <v>7</v>
+      </c>
+      <c r="G37" s="7">
+        <v>13</v>
+      </c>
+      <c r="H37" s="6">
         <v>1.85714286</v>
       </c>
       <c r="I37" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J37" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K37" s="8" t="n">
-        <v>1202.0</v>
-      </c>
-      <c r="L37" s="8" t="n">
-        <v>1202.0</v>
-      </c>
-      <c r="M37" s="6" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="N37" s="6" t="n">
-        <v>0.0</v>
+      <c r="J37" s="6">
+        <v>1</v>
+      </c>
+      <c r="K37" s="8">
+        <v>1202</v>
+      </c>
+      <c r="L37" s="8">
+        <v>1202</v>
+      </c>
+      <c r="M37" s="6">
+        <v>12</v>
+      </c>
+      <c r="N37" s="6">
+        <v>0</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>36</v>
@@ -2513,7 +2573,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>17</v>
       </c>
@@ -2529,13 +2589,13 @@
       <c r="E38" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F38" s="7" t="n">
-        <v>2372.0</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>2777.0</v>
-      </c>
-      <c r="H38" s="6" t="n">
+      <c r="F38" s="7">
+        <v>2372</v>
+      </c>
+      <c r="G38" s="7">
+        <v>2777</v>
+      </c>
+      <c r="H38" s="6">
         <v>1.17074199</v>
       </c>
       <c r="I38" s="6" t="s">
@@ -2544,17 +2604,17 @@
       <c r="J38" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K38" s="8" t="n">
-        <v>36377.0</v>
+      <c r="K38" s="8">
+        <v>36377</v>
       </c>
       <c r="L38" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M38" s="6" t="n">
-        <v>2770.0</v>
-      </c>
-      <c r="N38" s="6" t="n">
-        <v>11.0</v>
+      <c r="M38" s="6">
+        <v>2770</v>
+      </c>
+      <c r="N38" s="6">
+        <v>11</v>
       </c>
       <c r="O38" s="9" t="s">
         <v>36</v>
@@ -2566,7 +2626,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>17</v>
       </c>
@@ -2582,14 +2642,14 @@
       <c r="E39" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F39" s="7" t="n">
-        <v>48.0</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>61.0</v>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v>1.27083333</v>
+      <c r="F39" s="7">
+        <v>48</v>
+      </c>
+      <c r="G39" s="7">
+        <v>61</v>
+      </c>
+      <c r="H39" s="6">
+        <v>1.2708333300000001</v>
       </c>
       <c r="I39" s="6" t="s">
         <v>22</v>
@@ -2597,17 +2657,17 @@
       <c r="J39" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K39" s="8" t="n">
-        <v>2763.0</v>
+      <c r="K39" s="8">
+        <v>2763</v>
       </c>
       <c r="L39" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M39" s="6" t="n">
-        <v>57.0</v>
-      </c>
-      <c r="N39" s="6" t="n">
-        <v>0.0</v>
+      <c r="M39" s="6">
+        <v>57</v>
+      </c>
+      <c r="N39" s="6">
+        <v>0</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>36</v>
@@ -2619,7 +2679,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>17</v>
       </c>
@@ -2635,14 +2695,14 @@
       <c r="E40" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F40" s="7" t="n">
-        <v>242.0</v>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>261.0</v>
-      </c>
-      <c r="H40" s="6" t="n">
-        <v>1.0785124</v>
+      <c r="F40" s="7">
+        <v>242</v>
+      </c>
+      <c r="G40" s="7">
+        <v>261</v>
+      </c>
+      <c r="H40" s="6">
+        <v>1.0785123999999999</v>
       </c>
       <c r="I40" s="6" t="s">
         <v>22</v>
@@ -2650,17 +2710,17 @@
       <c r="J40" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K40" s="8" t="n">
-        <v>8247.0</v>
+      <c r="K40" s="8">
+        <v>8247</v>
       </c>
       <c r="L40" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M40" s="6" t="n">
-        <v>271.0</v>
-      </c>
-      <c r="N40" s="6" t="n">
-        <v>9.0</v>
+      <c r="M40" s="6">
+        <v>271</v>
+      </c>
+      <c r="N40" s="6">
+        <v>9</v>
       </c>
       <c r="O40" s="9" t="s">
         <v>36</v>
@@ -2672,7 +2732,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>17</v>
       </c>
@@ -2688,32 +2748,32 @@
       <c r="E41" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F41" s="7" t="n">
-        <v>975.0</v>
-      </c>
-      <c r="G41" s="7" t="n">
-        <v>1141.0</v>
-      </c>
-      <c r="H41" s="6" t="n">
-        <v>1.17025641</v>
+      <c r="F41" s="7">
+        <v>975</v>
+      </c>
+      <c r="G41" s="7">
+        <v>1141</v>
+      </c>
+      <c r="H41" s="6">
+        <v>1.1702564099999999</v>
       </c>
       <c r="I41" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J41" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K41" s="8" t="n">
-        <v>32077.0</v>
-      </c>
-      <c r="L41" s="8" t="n">
-        <v>32077.0</v>
-      </c>
-      <c r="M41" s="6" t="n">
-        <v>1157.0</v>
-      </c>
-      <c r="N41" s="6" t="n">
-        <v>11.0</v>
+      <c r="J41" s="6">
+        <v>1</v>
+      </c>
+      <c r="K41" s="8">
+        <v>32077</v>
+      </c>
+      <c r="L41" s="8">
+        <v>32077</v>
+      </c>
+      <c r="M41" s="6">
+        <v>1157</v>
+      </c>
+      <c r="N41" s="6">
+        <v>11</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>37</v>
@@ -2725,7 +2785,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>17</v>
       </c>
@@ -2741,13 +2801,13 @@
       <c r="E42" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F42" s="7" t="n">
-        <v>315.0</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>434.0</v>
-      </c>
-      <c r="H42" s="6" t="n">
+      <c r="F42" s="7">
+        <v>315</v>
+      </c>
+      <c r="G42" s="7">
+        <v>434</v>
+      </c>
+      <c r="H42" s="6">
         <v>1.37777778</v>
       </c>
       <c r="I42" s="6" t="s">
@@ -2756,17 +2816,17 @@
       <c r="J42" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K42" s="8" t="n">
-        <v>30212.0</v>
+      <c r="K42" s="8">
+        <v>30212</v>
       </c>
       <c r="L42" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M42" s="6" t="n">
-        <v>427.0</v>
-      </c>
-      <c r="N42" s="6" t="n">
-        <v>13.0</v>
+      <c r="M42" s="6">
+        <v>427</v>
+      </c>
+      <c r="N42" s="6">
+        <v>13</v>
       </c>
       <c r="O42" s="9" t="s">
         <v>37</v>
@@ -2778,7 +2838,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>17</v>
       </c>
@@ -2794,14 +2854,14 @@
       <c r="E43" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F43" s="7" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="G43" s="7" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="H43" s="6" t="n">
-        <v>1.05263158</v>
+      <c r="F43" s="7">
+        <v>19</v>
+      </c>
+      <c r="G43" s="7">
+        <v>20</v>
+      </c>
+      <c r="H43" s="6">
+        <v>1.0526315799999999</v>
       </c>
       <c r="I43" s="6" t="s">
         <v>22</v>
@@ -2809,17 +2869,17 @@
       <c r="J43" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K43" s="8" t="n">
-        <v>1360.0</v>
+      <c r="K43" s="8">
+        <v>1360</v>
       </c>
       <c r="L43" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M43" s="6" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="N43" s="6" t="n">
-        <v>0.0</v>
+      <c r="M43" s="6">
+        <v>19</v>
+      </c>
+      <c r="N43" s="6">
+        <v>0</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>37</v>
@@ -2831,7 +2891,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>17</v>
       </c>
@@ -2847,13 +2907,13 @@
       <c r="E44" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F44" s="7" t="n">
-        <v>34.0</v>
-      </c>
-      <c r="G44" s="7" t="n">
-        <v>46.0</v>
-      </c>
-      <c r="H44" s="6" t="n">
+      <c r="F44" s="7">
+        <v>34</v>
+      </c>
+      <c r="G44" s="7">
+        <v>46</v>
+      </c>
+      <c r="H44" s="6">
         <v>1.35294118</v>
       </c>
       <c r="I44" s="6" t="s">
@@ -2862,17 +2922,17 @@
       <c r="J44" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K44" s="8" t="n">
-        <v>2593.0</v>
+      <c r="K44" s="8">
+        <v>2593</v>
       </c>
       <c r="L44" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M44" s="6" t="n">
-        <v>46.0</v>
-      </c>
-      <c r="N44" s="6" t="n">
-        <v>4.0</v>
+      <c r="M44" s="6">
+        <v>46</v>
+      </c>
+      <c r="N44" s="6">
+        <v>4</v>
       </c>
       <c r="O44" s="9" t="s">
         <v>37</v>
@@ -2884,7 +2944,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>17</v>
       </c>
@@ -2900,13 +2960,13 @@
       <c r="E45" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="7" t="n">
-        <v>200.0</v>
-      </c>
-      <c r="G45" s="7" t="n">
-        <v>206.0</v>
-      </c>
-      <c r="H45" s="6" t="n">
+      <c r="F45" s="7">
+        <v>200</v>
+      </c>
+      <c r="G45" s="7">
+        <v>206</v>
+      </c>
+      <c r="H45" s="6">
         <v>1.03</v>
       </c>
       <c r="I45" s="6" t="s">
@@ -2915,17 +2975,17 @@
       <c r="J45" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K45" s="8" t="n">
-        <v>6903.0</v>
+      <c r="K45" s="8">
+        <v>6903</v>
       </c>
       <c r="L45" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M45" s="6" t="n">
-        <v>202.0</v>
-      </c>
-      <c r="N45" s="6" t="n">
-        <v>8.0</v>
+      <c r="M45" s="6">
+        <v>202</v>
+      </c>
+      <c r="N45" s="6">
+        <v>8</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>37</v>
@@ -2937,7 +2997,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>17</v>
       </c>
@@ -2953,13 +3013,13 @@
       <c r="E46" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F46" s="7" t="n">
-        <v>516.0</v>
-      </c>
-      <c r="G46" s="7" t="n">
-        <v>665.0</v>
-      </c>
-      <c r="H46" s="6" t="n">
+      <c r="F46" s="7">
+        <v>516</v>
+      </c>
+      <c r="G46" s="7">
+        <v>665</v>
+      </c>
+      <c r="H46" s="6">
         <v>1.28875969</v>
       </c>
       <c r="I46" s="6" t="s">
@@ -2968,17 +3028,17 @@
       <c r="J46" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K46" s="8" t="n">
-        <v>46457.0</v>
+      <c r="K46" s="8">
+        <v>46457</v>
       </c>
       <c r="L46" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M46" s="6" t="n">
-        <v>660.0</v>
-      </c>
-      <c r="N46" s="6" t="n">
-        <v>14.0</v>
+      <c r="M46" s="6">
+        <v>660</v>
+      </c>
+      <c r="N46" s="6">
+        <v>14</v>
       </c>
       <c r="O46" s="9" t="s">
         <v>38</v>
@@ -2990,7 +3050,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>17</v>
       </c>
@@ -3006,32 +3066,32 @@
       <c r="E47" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F47" s="7" t="n">
-        <v>23.0</v>
-      </c>
-      <c r="G47" s="7" t="n">
-        <v>33.0</v>
-      </c>
-      <c r="H47" s="6" t="n">
-        <v>1.43478261</v>
+      <c r="F47" s="7">
+        <v>23</v>
+      </c>
+      <c r="G47" s="7">
+        <v>33</v>
+      </c>
+      <c r="H47" s="6">
+        <v>1.4347826100000001</v>
       </c>
       <c r="I47" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J47" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K47" s="8" t="n">
-        <v>3845.0</v>
-      </c>
-      <c r="L47" s="8" t="n">
-        <v>3845.0</v>
-      </c>
-      <c r="M47" s="6" t="n">
-        <v>31.0</v>
-      </c>
-      <c r="N47" s="6" t="n">
-        <v>0.0</v>
+      <c r="J47" s="6">
+        <v>1</v>
+      </c>
+      <c r="K47" s="8">
+        <v>3845</v>
+      </c>
+      <c r="L47" s="8">
+        <v>3845</v>
+      </c>
+      <c r="M47" s="6">
+        <v>31</v>
+      </c>
+      <c r="N47" s="6">
+        <v>0</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>38</v>
@@ -3043,7 +3103,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>17</v>
       </c>
@@ -3059,32 +3119,32 @@
       <c r="E48" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F48" s="7" t="n">
-        <v>649.0</v>
-      </c>
-      <c r="G48" s="7" t="n">
-        <v>812.0</v>
-      </c>
-      <c r="H48" s="6" t="n">
+      <c r="F48" s="7">
+        <v>649</v>
+      </c>
+      <c r="G48" s="7">
+        <v>812</v>
+      </c>
+      <c r="H48" s="6">
         <v>1.25115562</v>
       </c>
       <c r="I48" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J48" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K48" s="8" t="n">
-        <v>16538.0</v>
-      </c>
-      <c r="L48" s="8" t="n">
-        <v>16538.0</v>
-      </c>
-      <c r="M48" s="6" t="n">
-        <v>820.0</v>
-      </c>
-      <c r="N48" s="6" t="n">
-        <v>9.0</v>
+      <c r="J48" s="6">
+        <v>1</v>
+      </c>
+      <c r="K48" s="8">
+        <v>16538</v>
+      </c>
+      <c r="L48" s="8">
+        <v>16538</v>
+      </c>
+      <c r="M48" s="6">
+        <v>820</v>
+      </c>
+      <c r="N48" s="6">
+        <v>9</v>
       </c>
       <c r="O48" s="9" t="s">
         <v>38</v>
@@ -3096,7 +3156,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>17</v>
       </c>
@@ -3112,32 +3172,32 @@
       <c r="E49" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F49" s="7" t="n">
-        <v>55.0</v>
-      </c>
-      <c r="G49" s="7" t="n">
-        <v>82.0</v>
-      </c>
-      <c r="H49" s="6" t="n">
-        <v>1.49090909</v>
+      <c r="F49" s="7">
+        <v>55</v>
+      </c>
+      <c r="G49" s="7">
+        <v>82</v>
+      </c>
+      <c r="H49" s="6">
+        <v>1.4909090899999999</v>
       </c>
       <c r="I49" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J49" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K49" s="8" t="n">
-        <v>3542.0</v>
-      </c>
-      <c r="L49" s="8" t="n">
-        <v>3542.0</v>
-      </c>
-      <c r="M49" s="6" t="n">
-        <v>74.0</v>
-      </c>
-      <c r="N49" s="6" t="n">
-        <v>3.0</v>
+      <c r="J49" s="6">
+        <v>1</v>
+      </c>
+      <c r="K49" s="8">
+        <v>3542</v>
+      </c>
+      <c r="L49" s="8">
+        <v>3542</v>
+      </c>
+      <c r="M49" s="6">
+        <v>74</v>
+      </c>
+      <c r="N49" s="6">
+        <v>3</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>38</v>
@@ -3149,7 +3209,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>17</v>
       </c>
@@ -3165,14 +3225,14 @@
       <c r="E50" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F50" s="7" t="n">
-        <v>173.0</v>
-      </c>
-      <c r="G50" s="7" t="n">
-        <v>192.0</v>
-      </c>
-      <c r="H50" s="6" t="n">
-        <v>1.10982659</v>
+      <c r="F50" s="7">
+        <v>173</v>
+      </c>
+      <c r="G50" s="7">
+        <v>192</v>
+      </c>
+      <c r="H50" s="6">
+        <v>1.1098265899999999</v>
       </c>
       <c r="I50" s="6" t="s">
         <v>22</v>
@@ -3180,17 +3240,17 @@
       <c r="J50" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K50" s="8" t="n">
-        <v>9375.0</v>
+      <c r="K50" s="8">
+        <v>9375</v>
       </c>
       <c r="L50" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M50" s="6" t="n">
-        <v>199.0</v>
-      </c>
-      <c r="N50" s="6" t="n">
-        <v>3.0</v>
+      <c r="M50" s="6">
+        <v>199</v>
+      </c>
+      <c r="N50" s="6">
+        <v>3</v>
       </c>
       <c r="O50" s="9" t="s">
         <v>38</v>
@@ -3202,7 +3262,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>17</v>
       </c>
@@ -3218,13 +3278,13 @@
       <c r="E51" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="7" t="n">
-        <v>49.0</v>
-      </c>
-      <c r="G51" s="7" t="n">
-        <v>80.0</v>
-      </c>
-      <c r="H51" s="6" t="n">
+      <c r="F51" s="7">
+        <v>49</v>
+      </c>
+      <c r="G51" s="7">
+        <v>80</v>
+      </c>
+      <c r="H51" s="6">
         <v>1.63265306</v>
       </c>
       <c r="I51" s="6" t="s">
@@ -3233,17 +3293,17 @@
       <c r="J51" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K51" s="8" t="n">
-        <v>4245.0</v>
+      <c r="K51" s="8">
+        <v>4245</v>
       </c>
       <c r="L51" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M51" s="6" t="n">
-        <v>79.0</v>
-      </c>
-      <c r="N51" s="6" t="n">
-        <v>2.0</v>
+      <c r="M51" s="6">
+        <v>79</v>
+      </c>
+      <c r="N51" s="6">
+        <v>2</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>39</v>
@@ -3255,7 +3315,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>17</v>
       </c>
@@ -3271,13 +3331,13 @@
       <c r="E52" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F52" s="7" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="G52" s="7" t="n">
-        <v>274.0</v>
-      </c>
-      <c r="H52" s="6" t="n">
+      <c r="F52" s="7">
+        <v>240</v>
+      </c>
+      <c r="G52" s="7">
+        <v>274</v>
+      </c>
+      <c r="H52" s="6">
         <v>1.14166667</v>
       </c>
       <c r="I52" s="6" t="s">
@@ -3286,17 +3346,17 @@
       <c r="J52" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K52" s="8" t="n">
-        <v>7303.0</v>
+      <c r="K52" s="8">
+        <v>7303</v>
       </c>
       <c r="L52" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M52" s="6" t="n">
-        <v>273.0</v>
-      </c>
-      <c r="N52" s="6" t="n">
-        <v>3.0</v>
+      <c r="M52" s="6">
+        <v>273</v>
+      </c>
+      <c r="N52" s="6">
+        <v>3</v>
       </c>
       <c r="O52" s="9" t="s">
         <v>39</v>
@@ -3308,7 +3368,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>17</v>
       </c>
@@ -3324,32 +3384,32 @@
       <c r="E53" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F53" s="7" t="n">
-        <v>747.0</v>
-      </c>
-      <c r="G53" s="7" t="n">
-        <v>945.0</v>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>1.26506024</v>
+      <c r="F53" s="7">
+        <v>747</v>
+      </c>
+      <c r="G53" s="7">
+        <v>945</v>
+      </c>
+      <c r="H53" s="6">
+        <v>1.2650602399999999</v>
       </c>
       <c r="I53" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J53" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K53" s="8" t="n">
-        <v>14376.0</v>
-      </c>
-      <c r="L53" s="8" t="n">
-        <v>14376.0</v>
-      </c>
-      <c r="M53" s="6" t="n">
-        <v>945.0</v>
-      </c>
-      <c r="N53" s="6" t="n">
-        <v>10.0</v>
+      <c r="J53" s="6">
+        <v>1</v>
+      </c>
+      <c r="K53" s="8">
+        <v>14376</v>
+      </c>
+      <c r="L53" s="8">
+        <v>14376</v>
+      </c>
+      <c r="M53" s="6">
+        <v>945</v>
+      </c>
+      <c r="N53" s="6">
+        <v>10</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>39</v>
@@ -3361,7 +3421,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>17</v>
       </c>
@@ -3377,14 +3437,14 @@
       <c r="E54" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F54" s="7" t="n">
-        <v>47.0</v>
-      </c>
-      <c r="G54" s="7" t="n">
-        <v>67.0</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>1.42553191</v>
+      <c r="F54" s="7">
+        <v>47</v>
+      </c>
+      <c r="G54" s="7">
+        <v>67</v>
+      </c>
+      <c r="H54" s="6">
+        <v>1.4255319099999999</v>
       </c>
       <c r="I54" s="6" t="s">
         <v>22</v>
@@ -3392,17 +3452,17 @@
       <c r="J54" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K54" s="8" t="n">
-        <v>2791.0</v>
+      <c r="K54" s="8">
+        <v>2791</v>
       </c>
       <c r="L54" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M54" s="6" t="n">
-        <v>67.0</v>
-      </c>
-      <c r="N54" s="6" t="n">
-        <v>3.0</v>
+      <c r="M54" s="6">
+        <v>67</v>
+      </c>
+      <c r="N54" s="6">
+        <v>3</v>
       </c>
       <c r="O54" s="9" t="s">
         <v>39</v>
@@ -3414,7 +3474,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>17</v>
       </c>
@@ -3430,14 +3490,14 @@
       <c r="E55" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F55" s="7" t="n">
-        <v>499.0</v>
-      </c>
-      <c r="G55" s="7" t="n">
-        <v>679.0</v>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>1.36072144</v>
+      <c r="F55" s="7">
+        <v>499</v>
+      </c>
+      <c r="G55" s="7">
+        <v>679</v>
+      </c>
+      <c r="H55" s="6">
+        <v>1.3607214400000001</v>
       </c>
       <c r="I55" s="6" t="s">
         <v>22</v>
@@ -3445,17 +3505,17 @@
       <c r="J55" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K55" s="8" t="n">
-        <v>39445.0</v>
+      <c r="K55" s="8">
+        <v>689000</v>
       </c>
       <c r="L55" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M55" s="6" t="n">
-        <v>701.0</v>
-      </c>
-      <c r="N55" s="6" t="n">
-        <v>14.0</v>
+      <c r="M55" s="6">
+        <v>701</v>
+      </c>
+      <c r="N55" s="6">
+        <v>14</v>
       </c>
       <c r="O55" s="9" t="s">
         <v>39</v>
@@ -3467,7 +3527,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>17</v>
       </c>
@@ -3483,32 +3543,32 @@
       <c r="E56" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F56" s="7" t="n">
-        <v>313.0</v>
-      </c>
-      <c r="G56" s="7" t="n">
-        <v>468.0</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>1.49520767</v>
+      <c r="F56" s="7">
+        <v>313</v>
+      </c>
+      <c r="G56" s="7">
+        <v>468</v>
+      </c>
+      <c r="H56" s="6">
+        <v>1.4952076700000001</v>
       </c>
       <c r="I56" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J56" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K56" s="8" t="n">
-        <v>50121.0</v>
-      </c>
-      <c r="L56" s="8" t="n">
-        <v>50121.0</v>
-      </c>
-      <c r="M56" s="6" t="n">
-        <v>477.0</v>
-      </c>
-      <c r="N56" s="6" t="n">
-        <v>18.0</v>
+      <c r="J56" s="6">
+        <v>1</v>
+      </c>
+      <c r="K56" s="8">
+        <v>50121</v>
+      </c>
+      <c r="L56" s="8">
+        <v>50121</v>
+      </c>
+      <c r="M56" s="6">
+        <v>477</v>
+      </c>
+      <c r="N56" s="6">
+        <v>18</v>
       </c>
       <c r="O56" s="9" t="s">
         <v>40</v>
@@ -3520,7 +3580,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>17</v>
       </c>
@@ -3536,32 +3596,32 @@
       <c r="E57" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F57" s="7" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="G57" s="7" t="n">
-        <v>47.0</v>
-      </c>
-      <c r="H57" s="6" t="n">
+      <c r="F57" s="7">
+        <v>25</v>
+      </c>
+      <c r="G57" s="7">
+        <v>47</v>
+      </c>
+      <c r="H57" s="6">
         <v>1.88</v>
       </c>
       <c r="I57" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J57" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K57" s="8" t="n">
-        <v>4492.0</v>
-      </c>
-      <c r="L57" s="8" t="n">
-        <v>4492.0</v>
-      </c>
-      <c r="M57" s="6" t="n">
-        <v>45.0</v>
-      </c>
-      <c r="N57" s="6" t="n">
-        <v>5.0</v>
+      <c r="J57" s="6">
+        <v>1</v>
+      </c>
+      <c r="K57" s="8">
+        <v>4492</v>
+      </c>
+      <c r="L57" s="8">
+        <v>4492</v>
+      </c>
+      <c r="M57" s="6">
+        <v>45</v>
+      </c>
+      <c r="N57" s="6">
+        <v>5</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>40</v>
@@ -3573,7 +3633,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>17</v>
       </c>
@@ -3589,14 +3649,14 @@
       <c r="E58" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F58" s="7" t="n">
-        <v>546.0</v>
-      </c>
-      <c r="G58" s="7" t="n">
-        <v>655.0</v>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>1.1996337</v>
+      <c r="F58" s="7">
+        <v>546</v>
+      </c>
+      <c r="G58" s="7">
+        <v>655</v>
+      </c>
+      <c r="H58" s="6">
+        <v>1.1996336999999999</v>
       </c>
       <c r="I58" s="6" t="s">
         <v>22</v>
@@ -3604,17 +3664,17 @@
       <c r="J58" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K58" s="8" t="n">
-        <v>11418.0</v>
+      <c r="K58" s="8">
+        <v>11418</v>
       </c>
       <c r="L58" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M58" s="6" t="n">
-        <v>651.0</v>
-      </c>
-      <c r="N58" s="6" t="n">
-        <v>2.0</v>
+      <c r="M58" s="6">
+        <v>651</v>
+      </c>
+      <c r="N58" s="6">
+        <v>2</v>
       </c>
       <c r="O58" s="9" t="s">
         <v>40</v>
@@ -3626,7 +3686,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>17</v>
       </c>
@@ -3642,32 +3702,32 @@
       <c r="E59" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F59" s="7" t="n">
-        <v>67.0</v>
-      </c>
-      <c r="G59" s="7" t="n">
-        <v>89.0</v>
-      </c>
-      <c r="H59" s="6" t="n">
+      <c r="F59" s="7">
+        <v>67</v>
+      </c>
+      <c r="G59" s="7">
+        <v>89</v>
+      </c>
+      <c r="H59" s="6">
         <v>1.32835821</v>
       </c>
       <c r="I59" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J59" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K59" s="8" t="n">
-        <v>6888.0</v>
-      </c>
-      <c r="L59" s="8" t="n">
-        <v>6888.0</v>
-      </c>
-      <c r="M59" s="6" t="n">
-        <v>85.0</v>
-      </c>
-      <c r="N59" s="6" t="n">
-        <v>1.0</v>
+      <c r="J59" s="6">
+        <v>1</v>
+      </c>
+      <c r="K59" s="8">
+        <v>6888</v>
+      </c>
+      <c r="L59" s="8">
+        <v>6888</v>
+      </c>
+      <c r="M59" s="6">
+        <v>85</v>
+      </c>
+      <c r="N59" s="6">
+        <v>1</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>40</v>
@@ -3679,7 +3739,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>17</v>
       </c>
@@ -3695,13 +3755,13 @@
       <c r="E60" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F60" s="7" t="n">
-        <v>135.0</v>
-      </c>
-      <c r="G60" s="7" t="n">
-        <v>157.0</v>
-      </c>
-      <c r="H60" s="6" t="n">
+      <c r="F60" s="7">
+        <v>135</v>
+      </c>
+      <c r="G60" s="7">
+        <v>157</v>
+      </c>
+      <c r="H60" s="6">
         <v>1.16296296</v>
       </c>
       <c r="I60" s="6" t="s">
@@ -3710,17 +3770,17 @@
       <c r="J60" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K60" s="8" t="n">
-        <v>7527.0</v>
+      <c r="K60" s="8">
+        <v>7527</v>
       </c>
       <c r="L60" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M60" s="6" t="n">
-        <v>163.0</v>
-      </c>
-      <c r="N60" s="6" t="n">
-        <v>3.0</v>
+      <c r="M60" s="6">
+        <v>163</v>
+      </c>
+      <c r="N60" s="6">
+        <v>3</v>
       </c>
       <c r="O60" s="9" t="s">
         <v>40</v>
@@ -3732,7 +3792,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>17</v>
       </c>
@@ -3748,14 +3808,14 @@
       <c r="E61" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F61" s="7" t="n">
-        <v>2490.0</v>
-      </c>
-      <c r="G61" s="7" t="n">
-        <v>3072.0</v>
-      </c>
-      <c r="H61" s="6" t="n">
-        <v>1.23373494</v>
+      <c r="F61" s="7">
+        <v>2490</v>
+      </c>
+      <c r="G61" s="7">
+        <v>3072</v>
+      </c>
+      <c r="H61" s="6">
+        <v>1.2337349399999999</v>
       </c>
       <c r="I61" s="6" t="s">
         <v>22</v>
@@ -3763,17 +3823,17 @@
       <c r="J61" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K61" s="8" t="n">
-        <v>34416.0</v>
+      <c r="K61" s="8">
+        <v>34416</v>
       </c>
       <c r="L61" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M61" s="6" t="n">
-        <v>3106.0</v>
-      </c>
-      <c r="N61" s="6" t="n">
-        <v>22.0</v>
+      <c r="M61" s="6">
+        <v>3106</v>
+      </c>
+      <c r="N61" s="6">
+        <v>22</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>41</v>
@@ -3785,7 +3845,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>17</v>
       </c>
@@ -3801,32 +3861,32 @@
       <c r="E62" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F62" s="7" t="n">
-        <v>237.0</v>
-      </c>
-      <c r="G62" s="7" t="n">
-        <v>268.0</v>
-      </c>
-      <c r="H62" s="6" t="n">
+      <c r="F62" s="7">
+        <v>237</v>
+      </c>
+      <c r="G62" s="7">
+        <v>268</v>
+      </c>
+      <c r="H62" s="6">
         <v>1.13080169</v>
       </c>
       <c r="I62" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J62" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K62" s="8" t="n">
-        <v>8374.0</v>
-      </c>
-      <c r="L62" s="8" t="n">
-        <v>8374.0</v>
-      </c>
-      <c r="M62" s="6" t="n">
-        <v>264.0</v>
-      </c>
-      <c r="N62" s="6" t="n">
-        <v>4.0</v>
+      <c r="J62" s="6">
+        <v>1</v>
+      </c>
+      <c r="K62" s="8">
+        <v>8374</v>
+      </c>
+      <c r="L62" s="8">
+        <v>8374</v>
+      </c>
+      <c r="M62" s="6">
+        <v>264</v>
+      </c>
+      <c r="N62" s="6">
+        <v>4</v>
       </c>
       <c r="O62" s="9" t="s">
         <v>41</v>
@@ -3838,7 +3898,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>17</v>
       </c>
@@ -3854,13 +3914,13 @@
       <c r="E63" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F63" s="7" t="n">
-        <v>49.0</v>
-      </c>
-      <c r="G63" s="7" t="n">
-        <v>85.0</v>
-      </c>
-      <c r="H63" s="6" t="n">
+      <c r="F63" s="7">
+        <v>49</v>
+      </c>
+      <c r="G63" s="7">
+        <v>85</v>
+      </c>
+      <c r="H63" s="6">
         <v>1.73469388</v>
       </c>
       <c r="I63" s="6" t="s">
@@ -3869,17 +3929,17 @@
       <c r="J63" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K63" s="8" t="n">
-        <v>3629.0</v>
+      <c r="K63" s="8">
+        <v>3629</v>
       </c>
       <c r="L63" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M63" s="6" t="n">
-        <v>77.0</v>
-      </c>
-      <c r="N63" s="6" t="n">
-        <v>0.0</v>
+      <c r="M63" s="6">
+        <v>77</v>
+      </c>
+      <c r="N63" s="6">
+        <v>0</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>41</v>
@@ -3891,7 +3951,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>17</v>
       </c>
@@ -3907,14 +3967,14 @@
       <c r="E64" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F64" s="7" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="G64" s="7" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="H64" s="6" t="n">
-        <v>1.33333333</v>
+      <c r="F64" s="7">
+        <v>12</v>
+      </c>
+      <c r="G64" s="7">
+        <v>16</v>
+      </c>
+      <c r="H64" s="6">
+        <v>1.3333333300000001</v>
       </c>
       <c r="I64" s="6" t="s">
         <v>22</v>
@@ -3922,17 +3982,17 @@
       <c r="J64" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K64" s="8" t="n">
-        <v>750.0</v>
+      <c r="K64" s="8">
+        <v>750</v>
       </c>
       <c r="L64" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M64" s="6" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="N64" s="6" t="n">
-        <v>0.0</v>
+      <c r="M64" s="6">
+        <v>14</v>
+      </c>
+      <c r="N64" s="6">
+        <v>0</v>
       </c>
       <c r="O64" s="9" t="s">
         <v>41</v>
@@ -3944,7 +4004,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>17</v>
       </c>
@@ -3960,32 +4020,32 @@
       <c r="E65" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F65" s="7" t="n">
-        <v>175.0</v>
-      </c>
-      <c r="G65" s="7" t="n">
-        <v>208.0</v>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>1.18857143</v>
+      <c r="F65" s="7">
+        <v>175</v>
+      </c>
+      <c r="G65" s="7">
+        <v>208</v>
+      </c>
+      <c r="H65" s="6">
+        <v>1.1885714300000001</v>
       </c>
       <c r="I65" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J65" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K65" s="8" t="n">
-        <v>8977.0</v>
-      </c>
-      <c r="L65" s="8" t="n">
-        <v>8977.0</v>
-      </c>
-      <c r="M65" s="6" t="n">
-        <v>203.0</v>
-      </c>
-      <c r="N65" s="6" t="n">
-        <v>5.0</v>
+      <c r="J65" s="6">
+        <v>1</v>
+      </c>
+      <c r="K65" s="8">
+        <v>8977</v>
+      </c>
+      <c r="L65" s="8">
+        <v>8977</v>
+      </c>
+      <c r="M65" s="6">
+        <v>203</v>
+      </c>
+      <c r="N65" s="6">
+        <v>5</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>41</v>
@@ -3997,7 +4057,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>17</v>
       </c>
@@ -4013,32 +4073,32 @@
       <c r="E66" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F66" s="7" t="n">
-        <v>2022.0</v>
-      </c>
-      <c r="G66" s="7" t="n">
-        <v>2708.0</v>
-      </c>
-      <c r="H66" s="6" t="n">
+      <c r="F66" s="7">
+        <v>2022</v>
+      </c>
+      <c r="G66" s="7">
+        <v>2708</v>
+      </c>
+      <c r="H66" s="6">
         <v>1.33926805</v>
       </c>
       <c r="I66" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J66" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K66" s="8" t="n">
-        <v>47339.0</v>
-      </c>
-      <c r="L66" s="8" t="n">
-        <v>47339.0</v>
-      </c>
-      <c r="M66" s="6" t="n">
-        <v>2724.0</v>
-      </c>
-      <c r="N66" s="6" t="n">
-        <v>25.0</v>
+      <c r="J66" s="6">
+        <v>1</v>
+      </c>
+      <c r="K66" s="8">
+        <v>875000</v>
+      </c>
+      <c r="L66" s="8">
+        <v>47339</v>
+      </c>
+      <c r="M66" s="6">
+        <v>2724</v>
+      </c>
+      <c r="N66" s="6">
+        <v>25</v>
       </c>
       <c r="O66" s="9" t="s">
         <v>42</v>
@@ -4050,7 +4110,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>17</v>
       </c>
@@ -4066,14 +4126,14 @@
       <c r="E67" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F67" s="7" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="G67" s="7" t="n">
-        <v>32.0</v>
-      </c>
-      <c r="H67" s="6" t="n">
-        <v>1.52380952</v>
+      <c r="F67" s="7">
+        <v>21</v>
+      </c>
+      <c r="G67" s="7">
+        <v>32</v>
+      </c>
+      <c r="H67" s="6">
+        <v>1.5238095199999999</v>
       </c>
       <c r="I67" s="6" t="s">
         <v>22</v>
@@ -4081,17 +4141,17 @@
       <c r="J67" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K67" s="8" t="n">
-        <v>888.0</v>
+      <c r="K67" s="8">
+        <v>888</v>
       </c>
       <c r="L67" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M67" s="6" t="n">
-        <v>29.0</v>
-      </c>
-      <c r="N67" s="6" t="n">
-        <v>0.0</v>
+      <c r="M67" s="6">
+        <v>29</v>
+      </c>
+      <c r="N67" s="6">
+        <v>0</v>
       </c>
       <c r="O67" s="9" t="s">
         <v>42</v>
@@ -4103,7 +4163,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>17</v>
       </c>
@@ -4119,32 +4179,32 @@
       <c r="E68" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F68" s="7" t="n">
-        <v>218.0</v>
-      </c>
-      <c r="G68" s="7" t="n">
-        <v>255.0</v>
-      </c>
-      <c r="H68" s="6" t="n">
+      <c r="F68" s="7">
+        <v>218</v>
+      </c>
+      <c r="G68" s="7">
+        <v>255</v>
+      </c>
+      <c r="H68" s="6">
         <v>1.16972477</v>
       </c>
       <c r="I68" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J68" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K68" s="8" t="n">
-        <v>7918.0</v>
-      </c>
-      <c r="L68" s="8" t="n">
-        <v>7918.0</v>
-      </c>
-      <c r="M68" s="6" t="n">
-        <v>261.0</v>
-      </c>
-      <c r="N68" s="6" t="n">
-        <v>16.0</v>
+      <c r="J68" s="6">
+        <v>1</v>
+      </c>
+      <c r="K68" s="8">
+        <v>7918</v>
+      </c>
+      <c r="L68" s="8">
+        <v>7918</v>
+      </c>
+      <c r="M68" s="6">
+        <v>261</v>
+      </c>
+      <c r="N68" s="6">
+        <v>16</v>
       </c>
       <c r="O68" s="9" t="s">
         <v>42</v>
@@ -4156,7 +4216,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>17</v>
       </c>
@@ -4172,32 +4232,32 @@
       <c r="E69" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F69" s="7" t="n">
-        <v>1929.0</v>
-      </c>
-      <c r="G69" s="7" t="n">
-        <v>2507.0</v>
-      </c>
-      <c r="H69" s="6" t="n">
-        <v>1.29963712</v>
+      <c r="F69" s="7">
+        <v>1929</v>
+      </c>
+      <c r="G69" s="7">
+        <v>2507</v>
+      </c>
+      <c r="H69" s="6">
+        <v>1.2996371200000001</v>
       </c>
       <c r="I69" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J69" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K69" s="8" t="n">
-        <v>51012.0</v>
-      </c>
-      <c r="L69" s="8" t="n">
-        <v>51012.0</v>
-      </c>
-      <c r="M69" s="6" t="n">
-        <v>2519.0</v>
-      </c>
-      <c r="N69" s="6" t="n">
-        <v>20.0</v>
+      <c r="J69" s="6">
+        <v>1</v>
+      </c>
+      <c r="K69" s="8">
+        <v>51012</v>
+      </c>
+      <c r="L69" s="8">
+        <v>51012</v>
+      </c>
+      <c r="M69" s="6">
+        <v>2519</v>
+      </c>
+      <c r="N69" s="6">
+        <v>20</v>
       </c>
       <c r="O69" s="9" t="s">
         <v>43</v>
@@ -4209,7 +4269,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>17</v>
       </c>
@@ -4225,14 +4285,14 @@
       <c r="E70" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F70" s="7" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="G70" s="7" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="H70" s="6" t="n">
-        <v>1.76470588</v>
+      <c r="F70" s="7">
+        <v>17</v>
+      </c>
+      <c r="G70" s="7">
+        <v>30</v>
+      </c>
+      <c r="H70" s="6">
+        <v>1.7647058799999999</v>
       </c>
       <c r="I70" s="6" t="s">
         <v>22</v>
@@ -4240,17 +4300,17 @@
       <c r="J70" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K70" s="8" t="n">
-        <v>1391.0</v>
+      <c r="K70" s="8">
+        <v>1391</v>
       </c>
       <c r="L70" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M70" s="6" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="N70" s="6" t="n">
-        <v>1.0</v>
+      <c r="M70" s="6">
+        <v>30</v>
+      </c>
+      <c r="N70" s="6">
+        <v>1</v>
       </c>
       <c r="O70" s="9" t="s">
         <v>43</v>
@@ -4262,7 +4322,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>17</v>
       </c>
@@ -4278,14 +4338,14 @@
       <c r="E71" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F71" s="7" t="n">
-        <v>213.0</v>
-      </c>
-      <c r="G71" s="7" t="n">
-        <v>236.0</v>
-      </c>
-      <c r="H71" s="6" t="n">
-        <v>1.10798122</v>
+      <c r="F71" s="7">
+        <v>213</v>
+      </c>
+      <c r="G71" s="7">
+        <v>236</v>
+      </c>
+      <c r="H71" s="6">
+        <v>1.1079812200000001</v>
       </c>
       <c r="I71" s="6" t="s">
         <v>22</v>
@@ -4293,17 +4353,17 @@
       <c r="J71" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K71" s="8" t="n">
-        <v>9840.0</v>
+      <c r="K71" s="8">
+        <v>9840</v>
       </c>
       <c r="L71" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M71" s="6" t="n">
-        <v>228.0</v>
-      </c>
-      <c r="N71" s="6" t="n">
-        <v>3.0</v>
+      <c r="M71" s="6">
+        <v>228</v>
+      </c>
+      <c r="N71" s="6">
+        <v>3</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>43</v>
@@ -4315,7 +4375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>17</v>
       </c>
@@ -4331,32 +4391,32 @@
       <c r="E72" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F72" s="7" t="n">
-        <v>156.0</v>
-      </c>
-      <c r="G72" s="7" t="n">
-        <v>165.0</v>
-      </c>
-      <c r="H72" s="6" t="n">
+      <c r="F72" s="7">
+        <v>156</v>
+      </c>
+      <c r="G72" s="7">
+        <v>165</v>
+      </c>
+      <c r="H72" s="6">
         <v>1.05769231</v>
       </c>
       <c r="I72" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J72" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K72" s="8" t="n">
-        <v>10205.0</v>
-      </c>
-      <c r="L72" s="8" t="n">
-        <v>10205.0</v>
-      </c>
-      <c r="M72" s="6" t="n">
-        <v>167.0</v>
-      </c>
-      <c r="N72" s="6" t="n">
-        <v>3.0</v>
+      <c r="J72" s="6">
+        <v>1</v>
+      </c>
+      <c r="K72" s="8">
+        <v>10205</v>
+      </c>
+      <c r="L72" s="8">
+        <v>10205</v>
+      </c>
+      <c r="M72" s="6">
+        <v>167</v>
+      </c>
+      <c r="N72" s="6">
+        <v>3</v>
       </c>
       <c r="O72" s="9" t="s">
         <v>44</v>
@@ -4368,7 +4428,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>17</v>
       </c>
@@ -4384,13 +4444,13 @@
       <c r="E73" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F73" s="7" t="n">
-        <v>35.0</v>
-      </c>
-      <c r="G73" s="7" t="n">
-        <v>63.0</v>
-      </c>
-      <c r="H73" s="6" t="n">
+      <c r="F73" s="7">
+        <v>35</v>
+      </c>
+      <c r="G73" s="7">
+        <v>63</v>
+      </c>
+      <c r="H73" s="6">
         <v>1.8</v>
       </c>
       <c r="I73" s="6" t="s">
@@ -4399,17 +4459,17 @@
       <c r="J73" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K73" s="8" t="n">
-        <v>3127.0</v>
+      <c r="K73" s="8">
+        <v>3127</v>
       </c>
       <c r="L73" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M73" s="6" t="n">
-        <v>64.0</v>
-      </c>
-      <c r="N73" s="6" t="n">
-        <v>2.0</v>
+      <c r="M73" s="6">
+        <v>64</v>
+      </c>
+      <c r="N73" s="6">
+        <v>2</v>
       </c>
       <c r="O73" s="9" t="s">
         <v>44</v>
@@ -4421,7 +4481,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>17</v>
       </c>
@@ -4437,32 +4497,32 @@
       <c r="E74" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F74" s="7" t="n">
-        <v>1808.0</v>
-      </c>
-      <c r="G74" s="7" t="n">
-        <v>2425.0</v>
-      </c>
-      <c r="H74" s="6" t="n">
-        <v>1.34126106</v>
+      <c r="F74" s="7">
+        <v>1808</v>
+      </c>
+      <c r="G74" s="7">
+        <v>2425</v>
+      </c>
+      <c r="H74" s="6">
+        <v>1.3412610599999999</v>
       </c>
       <c r="I74" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J74" s="6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K74" s="8" t="n">
-        <v>66462.0</v>
-      </c>
-      <c r="L74" s="8" t="n">
-        <v>33231.0</v>
-      </c>
-      <c r="M74" s="6" t="n">
-        <v>2461.0</v>
-      </c>
-      <c r="N74" s="6" t="n">
-        <v>40.0</v>
+      <c r="J74" s="6">
+        <v>2</v>
+      </c>
+      <c r="K74" s="8">
+        <v>66462</v>
+      </c>
+      <c r="L74" s="8">
+        <v>33231</v>
+      </c>
+      <c r="M74" s="6">
+        <v>2461</v>
+      </c>
+      <c r="N74" s="6">
+        <v>40</v>
       </c>
       <c r="O74" s="9" t="s">
         <v>44</v>
@@ -4474,7 +4534,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>17</v>
       </c>
@@ -4490,32 +4550,32 @@
       <c r="E75" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F75" s="7" t="n">
-        <v>1404.0</v>
-      </c>
-      <c r="G75" s="7" t="n">
-        <v>1897.0</v>
-      </c>
-      <c r="H75" s="6" t="n">
+      <c r="F75" s="7">
+        <v>1404</v>
+      </c>
+      <c r="G75" s="7">
+        <v>1897</v>
+      </c>
+      <c r="H75" s="6">
         <v>1.3511396</v>
       </c>
       <c r="I75" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J75" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K75" s="8" t="n">
-        <v>76444.0</v>
-      </c>
-      <c r="L75" s="8" t="n">
-        <v>76444.0</v>
-      </c>
-      <c r="M75" s="6" t="n">
-        <v>1933.0</v>
-      </c>
-      <c r="N75" s="6" t="n">
-        <v>23.0</v>
+      <c r="J75" s="6">
+        <v>1</v>
+      </c>
+      <c r="K75" s="8">
+        <v>76444</v>
+      </c>
+      <c r="L75" s="8">
+        <v>76444</v>
+      </c>
+      <c r="M75" s="6">
+        <v>1933</v>
+      </c>
+      <c r="N75" s="6">
+        <v>23</v>
       </c>
       <c r="O75" s="9" t="s">
         <v>45</v>
@@ -4527,7 +4587,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>17</v>
       </c>
@@ -4543,13 +4603,13 @@
       <c r="E76" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F76" s="7" t="n">
-        <v>88.0</v>
-      </c>
-      <c r="G76" s="7" t="n">
-        <v>143.0</v>
-      </c>
-      <c r="H76" s="6" t="n">
+      <c r="F76" s="7">
+        <v>88</v>
+      </c>
+      <c r="G76" s="7">
+        <v>143</v>
+      </c>
+      <c r="H76" s="6">
         <v>1.625</v>
       </c>
       <c r="I76" s="6" t="s">
@@ -4558,17 +4618,17 @@
       <c r="J76" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K76" s="8" t="n">
-        <v>8453.0</v>
+      <c r="K76" s="8">
+        <v>8453</v>
       </c>
       <c r="L76" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M76" s="6" t="n">
-        <v>136.0</v>
-      </c>
-      <c r="N76" s="6" t="n">
-        <v>0.0</v>
+      <c r="M76" s="6">
+        <v>136</v>
+      </c>
+      <c r="N76" s="6">
+        <v>0</v>
       </c>
       <c r="O76" s="9" t="s">
         <v>45</v>
@@ -4580,7 +4640,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>17</v>
       </c>
@@ -4596,13 +4656,13 @@
       <c r="E77" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F77" s="7" t="n">
-        <v>125.0</v>
-      </c>
-      <c r="G77" s="7" t="n">
-        <v>128.0</v>
-      </c>
-      <c r="H77" s="6" t="n">
+      <c r="F77" s="7">
+        <v>125</v>
+      </c>
+      <c r="G77" s="7">
+        <v>128</v>
+      </c>
+      <c r="H77" s="6">
         <v>1.024</v>
       </c>
       <c r="I77" s="6" t="s">
@@ -4611,17 +4671,17 @@
       <c r="J77" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K77" s="8" t="n">
-        <v>2913.0</v>
+      <c r="K77" s="8">
+        <v>2913</v>
       </c>
       <c r="L77" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M77" s="6" t="n">
-        <v>131.0</v>
-      </c>
-      <c r="N77" s="6" t="n">
-        <v>2.0</v>
+      <c r="M77" s="6">
+        <v>131</v>
+      </c>
+      <c r="N77" s="6">
+        <v>2</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>45</v>
@@ -4633,7 +4693,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>17</v>
       </c>
@@ -4649,14 +4709,14 @@
       <c r="E78" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F78" s="7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G78" s="7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="H78" s="6" t="n">
-        <v>1.0</v>
+      <c r="F78" s="7">
+        <v>2</v>
+      </c>
+      <c r="G78" s="7">
+        <v>2</v>
+      </c>
+      <c r="H78" s="6">
+        <v>1</v>
       </c>
       <c r="I78" s="6" t="s">
         <v>22</v>
@@ -4664,17 +4724,17 @@
       <c r="J78" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K78" s="8" t="n">
-        <v>1.0</v>
+      <c r="K78" s="8">
+        <v>1</v>
       </c>
       <c r="L78" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M78" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N78" s="6" t="n">
-        <v>0.0</v>
+      <c r="M78" s="6">
+        <v>1</v>
+      </c>
+      <c r="N78" s="6">
+        <v>0</v>
       </c>
       <c r="O78" s="9" t="s">
         <v>46</v>
@@ -4686,7 +4746,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>17</v>
       </c>
@@ -4702,32 +4762,32 @@
       <c r="E79" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F79" s="7" t="n">
-        <v>257.0</v>
-      </c>
-      <c r="G79" s="7" t="n">
-        <v>277.0</v>
-      </c>
-      <c r="H79" s="6" t="n">
-        <v>1.07782101</v>
+      <c r="F79" s="7">
+        <v>257</v>
+      </c>
+      <c r="G79" s="7">
+        <v>277</v>
+      </c>
+      <c r="H79" s="6">
+        <v>1.0778210100000001</v>
       </c>
       <c r="I79" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J79" s="6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K79" s="8" t="n">
-        <v>9600.0</v>
-      </c>
-      <c r="L79" s="8" t="n">
-        <v>4800.0</v>
-      </c>
-      <c r="M79" s="6" t="n">
-        <v>263.0</v>
-      </c>
-      <c r="N79" s="6" t="n">
-        <v>3.0</v>
+      <c r="J79" s="6">
+        <v>2</v>
+      </c>
+      <c r="K79" s="8">
+        <v>457000</v>
+      </c>
+      <c r="L79" s="8">
+        <v>4800</v>
+      </c>
+      <c r="M79" s="6">
+        <v>263</v>
+      </c>
+      <c r="N79" s="6">
+        <v>3</v>
       </c>
       <c r="O79" s="9" t="s">
         <v>47</v>
@@ -4739,7 +4799,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>17</v>
       </c>
@@ -4755,14 +4815,14 @@
       <c r="E80" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F80" s="7" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="G80" s="7" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="H80" s="6" t="n">
-        <v>1.13636364</v>
+      <c r="F80" s="7">
+        <v>89</v>
+      </c>
+      <c r="G80" s="7">
+        <v>25</v>
+      </c>
+      <c r="H80" s="6">
+        <v>1.1363636399999999</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>22</v>
@@ -4770,17 +4830,17 @@
       <c r="J80" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K80" s="8" t="n">
-        <v>2245.0</v>
+      <c r="K80" s="8">
+        <v>2245</v>
       </c>
       <c r="L80" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M80" s="6" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="N80" s="6" t="n">
-        <v>1.0</v>
+      <c r="M80" s="6">
+        <v>24</v>
+      </c>
+      <c r="N80" s="6">
+        <v>1</v>
       </c>
       <c r="O80" s="9" t="s">
         <v>47</v>
@@ -4792,7 +4852,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>17</v>
       </c>
@@ -4808,32 +4868,32 @@
       <c r="E81" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F81" s="7" t="n">
-        <v>1251.0</v>
-      </c>
-      <c r="G81" s="7" t="n">
-        <v>1482.0</v>
-      </c>
-      <c r="H81" s="6" t="n">
-        <v>1.18465228</v>
+      <c r="F81" s="7">
+        <v>1251</v>
+      </c>
+      <c r="G81" s="7">
+        <v>1482</v>
+      </c>
+      <c r="H81" s="6">
+        <v>1.1846522799999999</v>
       </c>
       <c r="I81" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J81" s="6" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="K81" s="8" t="n">
-        <v>48004.0</v>
-      </c>
-      <c r="L81" s="8" t="n">
-        <v>9600.8</v>
-      </c>
-      <c r="M81" s="6" t="n">
-        <v>1520.0</v>
-      </c>
-      <c r="N81" s="6" t="n">
-        <v>32.0</v>
+      <c r="J81" s="6">
+        <v>5</v>
+      </c>
+      <c r="K81" s="8">
+        <v>853000</v>
+      </c>
+      <c r="L81" s="8">
+        <v>9600.7999999999993</v>
+      </c>
+      <c r="M81" s="6">
+        <v>1520</v>
+      </c>
+      <c r="N81" s="6">
+        <v>32</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>47</v>
@@ -4845,7 +4905,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>17</v>
       </c>
@@ -4861,13 +4921,13 @@
       <c r="E82" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F82" s="7" t="n">
-        <v>4316.0</v>
-      </c>
-      <c r="G82" s="7" t="n">
-        <v>4801.0</v>
-      </c>
-      <c r="H82" s="6" t="n">
+      <c r="F82" s="7">
+        <v>4316</v>
+      </c>
+      <c r="G82" s="7">
+        <v>4801</v>
+      </c>
+      <c r="H82" s="6">
         <v>1.11237257</v>
       </c>
       <c r="I82" s="6" t="s">
@@ -4876,17 +4936,17 @@
       <c r="J82" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K82" s="8" t="n">
-        <v>93327.0</v>
+      <c r="K82" s="8">
+        <v>93327</v>
       </c>
       <c r="L82" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M82" s="6" t="n">
-        <v>4792.0</v>
-      </c>
-      <c r="N82" s="6" t="n">
-        <v>20.0</v>
+      <c r="M82" s="6">
+        <v>4792</v>
+      </c>
+      <c r="N82" s="6">
+        <v>20</v>
       </c>
       <c r="O82" s="9" t="s">
         <v>48</v>
@@ -4898,7 +4958,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>17</v>
       </c>
@@ -4914,13 +4974,13 @@
       <c r="E83" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F83" s="7" t="n">
-        <v>2835.0</v>
-      </c>
-      <c r="G83" s="7" t="n">
-        <v>3275.0</v>
-      </c>
-      <c r="H83" s="6" t="n">
+      <c r="F83" s="7">
+        <v>2835</v>
+      </c>
+      <c r="G83" s="7">
+        <v>3275</v>
+      </c>
+      <c r="H83" s="6">
         <v>1.15520282</v>
       </c>
       <c r="I83" s="6" t="s">
@@ -4929,17 +4989,17 @@
       <c r="J83" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K83" s="8" t="n">
-        <v>23244.0</v>
+      <c r="K83" s="8">
+        <v>23244</v>
       </c>
       <c r="L83" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M83" s="6" t="n">
-        <v>3202.0</v>
-      </c>
-      <c r="N83" s="6" t="n">
-        <v>18.0</v>
+      <c r="M83" s="6">
+        <v>3202</v>
+      </c>
+      <c r="N83" s="6">
+        <v>18</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>48</v>
@@ -4951,7 +5011,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>17</v>
       </c>
@@ -4967,32 +5027,32 @@
       <c r="E84" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F84" s="7" t="n">
-        <v>95.0</v>
-      </c>
-      <c r="G84" s="7" t="n">
-        <v>107.0</v>
-      </c>
-      <c r="H84" s="6" t="n">
+      <c r="F84" s="7">
+        <v>95</v>
+      </c>
+      <c r="G84" s="7">
+        <v>107</v>
+      </c>
+      <c r="H84" s="6">
         <v>1.12631579</v>
       </c>
       <c r="I84" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J84" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K84" s="8" t="n">
-        <v>3759.0</v>
-      </c>
-      <c r="L84" s="8" t="n">
-        <v>3759.0</v>
-      </c>
-      <c r="M84" s="6" t="n">
-        <v>111.0</v>
-      </c>
-      <c r="N84" s="6" t="n">
-        <v>4.0</v>
+      <c r="J84" s="6">
+        <v>1</v>
+      </c>
+      <c r="K84" s="8">
+        <v>3759</v>
+      </c>
+      <c r="L84" s="8">
+        <v>3759</v>
+      </c>
+      <c r="M84" s="6">
+        <v>111</v>
+      </c>
+      <c r="N84" s="6">
+        <v>4</v>
       </c>
       <c r="O84" s="9" t="s">
         <v>48</v>
@@ -5004,7 +5064,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>17</v>
       </c>
@@ -5020,14 +5080,14 @@
       <c r="E85" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F85" s="7" t="n">
-        <v>190.0</v>
-      </c>
-      <c r="G85" s="7" t="n">
-        <v>253.0</v>
-      </c>
-      <c r="H85" s="6" t="n">
-        <v>1.33157895</v>
+      <c r="F85" s="7">
+        <v>190</v>
+      </c>
+      <c r="G85" s="7">
+        <v>253</v>
+      </c>
+      <c r="H85" s="6">
+        <v>1.3315789499999999</v>
       </c>
       <c r="I85" s="6" t="s">
         <v>22</v>
@@ -5035,17 +5095,17 @@
       <c r="J85" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K85" s="8" t="n">
-        <v>12620.0</v>
+      <c r="K85" s="8">
+        <v>12620</v>
       </c>
       <c r="L85" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M85" s="6" t="n">
-        <v>256.0</v>
-      </c>
-      <c r="N85" s="6" t="n">
-        <v>3.0</v>
+      <c r="M85" s="6">
+        <v>256</v>
+      </c>
+      <c r="N85" s="6">
+        <v>3</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>49</v>
@@ -5057,7 +5117,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>17</v>
       </c>
@@ -5073,32 +5133,32 @@
       <c r="E86" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F86" s="7" t="n">
-        <v>2289.0</v>
-      </c>
-      <c r="G86" s="7" t="n">
-        <v>2765.0</v>
-      </c>
-      <c r="H86" s="6" t="n">
+      <c r="F86" s="7">
+        <v>2289</v>
+      </c>
+      <c r="G86" s="7">
+        <v>2765</v>
+      </c>
+      <c r="H86" s="6">
         <v>1.20795107</v>
       </c>
       <c r="I86" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J86" s="6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K86" s="8" t="n">
-        <v>38856.0</v>
-      </c>
-      <c r="L86" s="8" t="n">
-        <v>19428.0</v>
-      </c>
-      <c r="M86" s="6" t="n">
-        <v>2847.0</v>
-      </c>
-      <c r="N86" s="6" t="n">
-        <v>16.0</v>
+      <c r="J86" s="6">
+        <v>2</v>
+      </c>
+      <c r="K86" s="8">
+        <v>38856</v>
+      </c>
+      <c r="L86" s="8">
+        <v>19428</v>
+      </c>
+      <c r="M86" s="6">
+        <v>2847</v>
+      </c>
+      <c r="N86" s="6">
+        <v>16</v>
       </c>
       <c r="O86" s="9" t="s">
         <v>49</v>
@@ -5110,7 +5170,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>17</v>
       </c>
@@ -5126,14 +5186,14 @@
       <c r="E87" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F87" s="7" t="n">
-        <v>1051.0</v>
-      </c>
-      <c r="G87" s="7" t="n">
-        <v>1305.0</v>
-      </c>
-      <c r="H87" s="6" t="n">
-        <v>1.2416746</v>
+      <c r="F87" s="7">
+        <v>1051</v>
+      </c>
+      <c r="G87" s="7">
+        <v>1305</v>
+      </c>
+      <c r="H87" s="6">
+        <v>1.2416746000000001</v>
       </c>
       <c r="I87" s="6" t="s">
         <v>22</v>
@@ -5141,17 +5201,17 @@
       <c r="J87" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K87" s="8" t="n">
-        <v>41516.0</v>
+      <c r="K87" s="8">
+        <v>41516</v>
       </c>
       <c r="L87" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M87" s="6" t="n">
-        <v>1326.0</v>
-      </c>
-      <c r="N87" s="6" t="n">
-        <v>23.0</v>
+      <c r="M87" s="6">
+        <v>1326</v>
+      </c>
+      <c r="N87" s="6">
+        <v>23</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>49</v>
@@ -5164,7 +5224,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>